--- a/common/src/locales/Translations_CBR_main.xlsx
+++ b/common/src/locales/Translations_CBR_main.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="ixUDkdO+b7ymZjddKqctcAS2JPwY2Uk4AyQeSrJ+X8o="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="hMuo+ZChhbkuIptX3iBD0+0uV1S26WM7tfMvAI4riyQ="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2442" uniqueCount="2312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2472" uniqueCount="2342">
   <si>
     <t>Key</t>
   </si>
@@ -7070,7 +7070,7 @@
     <t>&amp;Advice and counselling - stress and trauma</t>
   </si>
   <si>
-    <t>risk.mental.requirement._$CounsellingOther</t>
+    <t>x</t>
   </si>
   <si>
     <t>Advice and counselling - other</t>
@@ -7176,6 +7176,96 @@
   </si>
   <si>
     <t>&amp;Add image if available</t>
+  </si>
+  <si>
+    <t>referral.safeGuardingObservation</t>
+  </si>
+  <si>
+    <t>Observation</t>
+  </si>
+  <si>
+    <t>&amp;Observation</t>
+  </si>
+  <si>
+    <t>referral.safeGuardingPersonInvolved</t>
+  </si>
+  <si>
+    <t>Person Involved</t>
+  </si>
+  <si>
+    <t>&amp;Person Involved</t>
+  </si>
+  <si>
+    <t>referral.safeGuardingActionNeeded</t>
+  </si>
+  <si>
+    <t>Actions Needed</t>
+  </si>
+  <si>
+    <t>&amp;Actions Needed</t>
+  </si>
+  <si>
+    <t>referral.signsOfHarm</t>
+  </si>
+  <si>
+    <t>Signs of Harm</t>
+  </si>
+  <si>
+    <t>&amp;Signs of Harm</t>
+  </si>
+  <si>
+    <t>referral.neglect</t>
+  </si>
+  <si>
+    <t>Neglect</t>
+  </si>
+  <si>
+    <t>&amp;Neglect</t>
+  </si>
+  <si>
+    <t>referral.unsafeBehaviour</t>
+  </si>
+  <si>
+    <t>Unsafe Behaviour</t>
+  </si>
+  <si>
+    <t>&amp;Unsafe Behaviour</t>
+  </si>
+  <si>
+    <t>referral.urgentAttention</t>
+  </si>
+  <si>
+    <t>Urgent Attention</t>
+  </si>
+  <si>
+    <t>&amp;Urgent Attention</t>
+  </si>
+  <si>
+    <t>referral.followUp</t>
+  </si>
+  <si>
+    <t>Follow-up</t>
+  </si>
+  <si>
+    <t>&amp;Follow-up</t>
+  </si>
+  <si>
+    <t>referral.documentationOnly</t>
+  </si>
+  <si>
+    <t>Documentation Only</t>
+  </si>
+  <si>
+    <t>&amp;Documentation Only</t>
+  </si>
+  <si>
+    <t>referral.safeGuardingVisit</t>
+  </si>
+  <si>
+    <t>Safe Guarding Visit</t>
+  </si>
+  <si>
+    <t>&amp;Safe Guarding Visit</t>
   </si>
 </sst>
 </file>
@@ -7292,7 +7382,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="31">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -7361,11 +7451,20 @@
     <xf borderId="0" fillId="8" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
+    <xf borderId="0" fillId="8" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
     <xf borderId="0" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="8" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -17633,7 +17732,7 @@
       </c>
     </row>
     <row r="802" ht="15.75" customHeight="1">
-      <c r="A802" s="25" t="s">
+      <c r="A802" s="26" t="s">
         <v>2276</v>
       </c>
       <c r="B802" s="8" t="s">
@@ -17754,37 +17853,137 @@
       </c>
     </row>
     <row r="813" ht="15.75" customHeight="1">
-      <c r="A813" s="26" t="s">
+      <c r="A813" s="27" t="s">
         <v>2306</v>
       </c>
-      <c r="B813" s="27" t="s">
+      <c r="B813" s="28" t="s">
         <v>2307</v>
       </c>
-      <c r="C813" s="27" t="s">
+      <c r="C813" s="28" t="s">
         <v>2308</v>
       </c>
     </row>
     <row r="814" ht="15.75" customHeight="1">
-      <c r="A814" s="26" t="s">
+      <c r="A814" s="27" t="s">
         <v>2309</v>
       </c>
-      <c r="B814" s="27" t="s">
+      <c r="B814" s="28" t="s">
         <v>2310</v>
       </c>
-      <c r="C814" s="27" t="s">
+      <c r="C814" s="28" t="s">
         <v>2311</v>
       </c>
     </row>
-    <row r="815" ht="15.75" customHeight="1"/>
-    <row r="816" ht="15.75" customHeight="1"/>
-    <row r="817" ht="15.75" customHeight="1"/>
-    <row r="818" ht="15.75" customHeight="1"/>
-    <row r="819" ht="15.75" customHeight="1"/>
-    <row r="820" ht="15.75" customHeight="1"/>
-    <row r="821" ht="15.75" customHeight="1"/>
-    <row r="822" ht="15.75" customHeight="1"/>
-    <row r="823" ht="15.75" customHeight="1"/>
-    <row r="824" ht="15.75" customHeight="1"/>
+    <row r="815" ht="15.75" customHeight="1">
+      <c r="A815" s="29" t="s">
+        <v>2312</v>
+      </c>
+      <c r="B815" s="30" t="s">
+        <v>2313</v>
+      </c>
+      <c r="C815" s="30" t="s">
+        <v>2314</v>
+      </c>
+    </row>
+    <row r="816" ht="15.75" customHeight="1">
+      <c r="A816" s="29" t="s">
+        <v>2315</v>
+      </c>
+      <c r="B816" s="30" t="s">
+        <v>2316</v>
+      </c>
+      <c r="C816" s="30" t="s">
+        <v>2317</v>
+      </c>
+    </row>
+    <row r="817" ht="15.75" customHeight="1">
+      <c r="A817" s="29" t="s">
+        <v>2318</v>
+      </c>
+      <c r="B817" s="30" t="s">
+        <v>2319</v>
+      </c>
+      <c r="C817" s="30" t="s">
+        <v>2320</v>
+      </c>
+    </row>
+    <row r="818" ht="15.75" customHeight="1">
+      <c r="A818" s="29" t="s">
+        <v>2321</v>
+      </c>
+      <c r="B818" s="30" t="s">
+        <v>2322</v>
+      </c>
+      <c r="C818" s="30" t="s">
+        <v>2323</v>
+      </c>
+    </row>
+    <row r="819" ht="15.75" customHeight="1">
+      <c r="A819" s="29" t="s">
+        <v>2324</v>
+      </c>
+      <c r="B819" s="30" t="s">
+        <v>2325</v>
+      </c>
+      <c r="C819" s="30" t="s">
+        <v>2326</v>
+      </c>
+    </row>
+    <row r="820" ht="15.75" customHeight="1">
+      <c r="A820" s="29" t="s">
+        <v>2327</v>
+      </c>
+      <c r="B820" s="30" t="s">
+        <v>2328</v>
+      </c>
+      <c r="C820" s="30" t="s">
+        <v>2329</v>
+      </c>
+    </row>
+    <row r="821" ht="15.75" customHeight="1">
+      <c r="A821" s="29" t="s">
+        <v>2330</v>
+      </c>
+      <c r="B821" s="30" t="s">
+        <v>2331</v>
+      </c>
+      <c r="C821" s="30" t="s">
+        <v>2332</v>
+      </c>
+    </row>
+    <row r="822" ht="15.75" customHeight="1">
+      <c r="A822" s="29" t="s">
+        <v>2333</v>
+      </c>
+      <c r="B822" s="30" t="s">
+        <v>2334</v>
+      </c>
+      <c r="C822" s="30" t="s">
+        <v>2335</v>
+      </c>
+    </row>
+    <row r="823" ht="15.75" customHeight="1">
+      <c r="A823" s="29" t="s">
+        <v>2336</v>
+      </c>
+      <c r="B823" s="30" t="s">
+        <v>2337</v>
+      </c>
+      <c r="C823" s="30" t="s">
+        <v>2338</v>
+      </c>
+    </row>
+    <row r="824" ht="15.75" customHeight="1">
+      <c r="A824" s="29" t="s">
+        <v>2339</v>
+      </c>
+      <c r="B824" s="30" t="s">
+        <v>2340</v>
+      </c>
+      <c r="C824" s="30" t="s">
+        <v>2341</v>
+      </c>
+    </row>
     <row r="825" ht="15.75" customHeight="1"/>
     <row r="826" ht="15.75" customHeight="1"/>
     <row r="827" ht="15.75" customHeight="1"/>
@@ -17891,9 +18090,8 @@
     <row r="928" ht="15.75" customHeight="1"/>
     <row r="929" ht="15.75" customHeight="1"/>
     <row r="930" ht="15.75" customHeight="1"/>
-    <row r="931" ht="15.75" customHeight="1"/>
   </sheetData>
-  <conditionalFormatting sqref="A1:A604 B568 A759:A764 A810:A811 A813:A931">
+  <conditionalFormatting sqref="A1:A604 B568 A759:A764 A810:A811 A813:A930">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>COUNTIF (A:A, A1)&gt;1</formula>
     </cfRule>

--- a/common/src/locales/Translations_CBR_main.xlsx
+++ b/common/src/locales/Translations_CBR_main.xlsx
@@ -7178,7 +7178,7 @@
     <t>&amp;Add image if available</t>
   </si>
   <si>
-    <t>referral.safeGuardingObservation</t>
+    <t>referral.safeguardingObservation</t>
   </si>
   <si>
     <t>Observation</t>
@@ -7187,7 +7187,7 @@
     <t>&amp;Observation</t>
   </si>
   <si>
-    <t>referral.safeGuardingPersonInvolved</t>
+    <t>referral.safeguardingPersonInvolved</t>
   </si>
   <si>
     <t>Person Involved</t>
@@ -7196,7 +7196,7 @@
     <t>&amp;Person Involved</t>
   </si>
   <si>
-    <t>referral.safeGuardingActionNeeded</t>
+    <t>referral.safeguardingActionNeeded</t>
   </si>
   <si>
     <t>Actions Needed</t>
@@ -7259,7 +7259,7 @@
     <t>&amp;Documentation Only</t>
   </si>
   <si>
-    <t>referral.safeGuardingVisit</t>
+    <t>referral.safeguardingVisit</t>
   </si>
   <si>
     <t>Safe Guarding Visit</t>
